--- a/artfynd/A 32140-2022 artfynd.xlsx
+++ b/artfynd/A 32140-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32140-2022 artfynd.xlsx
+++ b/artfynd/A 32140-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106233503</v>
+        <v>112129046</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,25 +710,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ö Granfallsmossen, Upl</t>
+          <t>Persbomossen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654948.808948243</v>
+        <v>654944</v>
       </c>
       <c r="R2" t="n">
-        <v>6675777.238779158</v>
+        <v>6675780</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +751,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fuktig granskog med en del tall. Pepprig papperssmak. Ingen vit mycelmatta.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +780,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,42 +798,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112072638</v>
+        <v>112129048</v>
       </c>
       <c r="B3" t="n">
-        <v>90836</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -847,14 +840,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Persbomossen, Upl</t>
+          <t>Persbo gruva, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654962</v>
+        <v>654842</v>
       </c>
       <c r="R3" t="n">
-        <v>6675742</v>
+        <v>6675852</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -881,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,15 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112072636</v>
+        <v>112128620</v>
       </c>
       <c r="B4" t="n">
-        <v>90836</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,33 +927,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -974,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654965</v>
+        <v>654939</v>
       </c>
       <c r="R4" t="n">
-        <v>6675722</v>
+        <v>6675770</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1004,22 +988,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fuktig granskog. Ljusgul mjölksaft som ej ändrar färg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,43 +1035,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112111596</v>
+        <v>112072636</v>
       </c>
       <c r="B5" t="n">
-        <v>99028</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1090,13 +1081,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654946</v>
+        <v>654965</v>
       </c>
       <c r="R5" t="n">
-        <v>6675743</v>
+        <v>6675723</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,22 +1111,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,37 +1153,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112111594</v>
+        <v>112072638</v>
       </c>
       <c r="B6" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1202,11 +1188,10 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1214,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654936</v>
+        <v>654962</v>
       </c>
       <c r="R6" t="n">
-        <v>6675837</v>
+        <v>6675742</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1244,22 +1229,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,16 +1274,11 @@
         <v>112111575</v>
       </c>
       <c r="B7" t="n">
-        <v>91626</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1311,12 +1291,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1405,37 +1385,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112111595</v>
+        <v>112129050</v>
       </c>
       <c r="B8" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1445,11 +1420,10 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1457,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654959</v>
+        <v>654924</v>
       </c>
       <c r="R8" t="n">
-        <v>6675760</v>
+        <v>6675762</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1487,22 +1461,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,45 +1503,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112128620</v>
+        <v>112129051</v>
       </c>
       <c r="B9" t="n">
-        <v>90519</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1576,7 +1549,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654939</v>
+        <v>654920</v>
       </c>
       <c r="R9" t="n">
         <v>6675770</v>
@@ -1611,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1621,12 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Fuktig granskog. Ljusgul mjölksaft som ej ändrar färg.</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1653,54 +1621,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112129089</v>
+        <v>112129055</v>
       </c>
       <c r="B10" t="n">
-        <v>99028</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Persbo gruva, Upl</t>
+          <t>Persbomossen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654896</v>
+        <v>654891</v>
       </c>
       <c r="R10" t="n">
-        <v>6675846</v>
+        <v>6675789</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1732,7 +1702,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1742,7 +1712,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,15 +1739,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112128596</v>
+        <v>112129056</v>
       </c>
       <c r="B11" t="n">
-        <v>56477</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,35 +1750,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1821,10 +1785,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654869</v>
+        <v>654852</v>
       </c>
       <c r="R11" t="n">
-        <v>6675890</v>
+        <v>6675907</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1856,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1866,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1893,15 +1857,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112128592</v>
+        <v>112129057</v>
       </c>
       <c r="B12" t="n">
-        <v>56477</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,21 +1868,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1931,24 +1890,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Persbo gruva, Upl</t>
+          <t>Persbomossen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>654847</v>
+        <v>654969</v>
       </c>
       <c r="R12" t="n">
-        <v>6675850</v>
+        <v>6675730</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1980,7 +1938,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1990,7 +1948,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2017,15 +1975,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112129086</v>
+        <v>112128590</v>
       </c>
       <c r="B13" t="n">
-        <v>99028</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,27 +1986,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2061,10 +2022,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654854</v>
+        <v>654853</v>
       </c>
       <c r="R13" t="n">
-        <v>6675896</v>
+        <v>6675824</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2096,7 +2057,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2106,7 +2067,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2133,15 +2094,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112129048</v>
+        <v>112128591</v>
       </c>
       <c r="B14" t="n">
-        <v>90865</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,34 +2105,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2184,13 +2145,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654843</v>
+        <v>654840</v>
       </c>
       <c r="R14" t="n">
-        <v>6675852</v>
+        <v>6675825</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2219,7 +2180,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2229,7 +2190,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Sitter på gammal död tall, flyger iväg när den upptäcker mig.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2256,15 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112129046</v>
+        <v>112128592</v>
       </c>
       <c r="B15" t="n">
-        <v>90865</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2272,45 +2233,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Persbomossen, Upl</t>
+          <t>Persbo gruva, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654944</v>
+        <v>654847</v>
       </c>
       <c r="R15" t="n">
-        <v>6675779</v>
+        <v>6675850</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2342,7 +2304,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2352,12 +2314,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Fuktig granskog med en del tall. Pepprig papperssmak. Ingen vit mycelmatta.</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2384,19 +2341,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112128590</v>
+        <v>112128596</v>
       </c>
       <c r="B16" t="n">
-        <v>56477</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2436,10 +2388,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654853</v>
+        <v>654869</v>
       </c>
       <c r="R16" t="n">
-        <v>6675824</v>
+        <v>6675890</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2471,7 +2423,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2481,7 +2433,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2508,15 +2460,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112129085</v>
+        <v>112128598</v>
       </c>
       <c r="B17" t="n">
-        <v>99028</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2524,27 +2471,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2552,10 +2507,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654896</v>
+        <v>654901</v>
       </c>
       <c r="R17" t="n">
-        <v>6675820</v>
+        <v>6675850</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2587,7 +2542,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2597,7 +2552,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2624,57 +2579,60 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112129088</v>
+        <v>106233503</v>
       </c>
       <c r="B18" t="n">
-        <v>99028</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Persbo gruva, Upl</t>
+          <t>Ö Granfallsmossen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654863</v>
+        <v>654949</v>
       </c>
       <c r="R18" t="n">
-        <v>6675903</v>
+        <v>6675777</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2698,22 +2656,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2023-01-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2023-01-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2722,6 +2670,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2740,37 +2689,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112129057</v>
+        <v>108444366</v>
       </c>
       <c r="B19" t="n">
-        <v>90874</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2780,24 +2724,25 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Persbomossen, Upl</t>
+          <t>Mumsarby, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654969</v>
+        <v>654970</v>
       </c>
       <c r="R19" t="n">
-        <v>6675730</v>
+        <v>6675844</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2821,22 +2766,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2845,6 +2780,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2863,64 +2799,60 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112129055</v>
+        <v>108444380</v>
       </c>
       <c r="B20" t="n">
-        <v>90874</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Persbomossen, Upl</t>
+          <t>Mumsarby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654891</v>
+        <v>654960</v>
       </c>
       <c r="R20" t="n">
-        <v>6675788</v>
+        <v>6675858</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2944,22 +2876,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2968,6 +2890,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2986,41 +2909,44 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112129090</v>
+        <v>112111592</v>
       </c>
       <c r="B21" t="n">
-        <v>99028</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3030,10 +2956,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654966</v>
+        <v>654973</v>
       </c>
       <c r="R21" t="n">
-        <v>6675754</v>
+        <v>6675841</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3060,22 +2986,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Räknade en och en på liten yta.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3102,51 +3033,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112128598</v>
+        <v>112111594</v>
       </c>
       <c r="B22" t="n">
-        <v>56477</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3154,10 +3080,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654901</v>
+        <v>654936</v>
       </c>
       <c r="R22" t="n">
-        <v>6675849</v>
+        <v>6675837</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3184,22 +3110,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3226,50 +3152,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112129051</v>
+        <v>112111595</v>
       </c>
       <c r="B23" t="n">
-        <v>90874</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3277,10 +3199,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654921</v>
+        <v>654959</v>
       </c>
       <c r="R23" t="n">
-        <v>6675770</v>
+        <v>6675760</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3307,22 +3229,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3349,37 +3271,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112129050</v>
+        <v>112129074</v>
       </c>
       <c r="B24" t="n">
-        <v>90874</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3389,10 +3306,11 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3400,10 +3318,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654924</v>
+        <v>654942</v>
       </c>
       <c r="R24" t="n">
-        <v>6675762</v>
+        <v>6675839</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3435,7 +3353,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3445,7 +3363,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3472,49 +3390,36 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112129074</v>
+        <v>112111596</v>
       </c>
       <c r="B25" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3524,13 +3429,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654942</v>
+        <v>654946</v>
       </c>
       <c r="R25" t="n">
-        <v>6675839</v>
+        <v>6675743</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3554,22 +3459,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3593,6 +3498,680 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>112129085</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>654896</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6675820</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>112129086</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Persbo gruva, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>654854</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6675896</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>112129087</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Persbo gruva, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>654854</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6675910</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>112129088</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Persbo gruva, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>654863</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6675903</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>112129089</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Persbo gruva, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>654895</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6675847</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>112129090</v>
+      </c>
+      <c r="B31" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>654966</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6675754</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32140-2022 artfynd.xlsx
+++ b/artfynd/A 32140-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129046</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -913,6 +923,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129048</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128620</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1150,6 +1170,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112072636</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1268,6 +1293,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112072638</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1382,6 +1412,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112111575</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1500,6 +1535,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129050</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1618,6 +1658,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129051</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1736,6 +1781,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129055</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1854,6 +1904,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129056</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1972,6 +2027,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129057</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2091,6 +2151,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128590</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2219,6 +2284,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128591</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2338,6 +2408,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128592</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2457,6 +2532,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128596</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2576,6 +2656,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128598</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2686,6 +2771,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106233503</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2796,6 +2886,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108444366</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2906,6 +3001,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108444380</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3030,6 +3130,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112111592</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3149,6 +3254,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112111594</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3268,6 +3378,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112111595</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3387,6 +3502,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129074</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3498,6 +3618,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112111596</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3609,6 +3734,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129085</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3720,6 +3850,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129086</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3839,6 +3974,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129087</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3950,6 +4090,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129088</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4061,6 +4206,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129089</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4172,8 +4322,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129090</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>